--- a/backend/sample_data/sample_model.xlsx
+++ b/backend/sample_data/sample_model.xlsx
@@ -414,190 +414,451 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:B19"/>
+  <dimension ref="A2:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Purchase Price</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>42500000</v>
+          <t>Building Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1200 Market Street</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Total Sources</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>$ Per Unit</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Total Purchase Price</t>
+          <t>Total Square Feet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42500000</v>
+        <v>145000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Price / SF</t>
+          <t>Current Occupancy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>293.1</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Debt Proceeds</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>25500000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>176</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Going-In Cap Rate</t>
+          <t>Occupancy at Exit</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0525</v>
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Total Sources</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Exit Cap Rate</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.0575</v>
+          <t>Projected Hold Period</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5 Years</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Leverage</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.6</v>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gross</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>$ Per Unit</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Total Uses</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>$ Per Unit</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Purchase Price</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.055</v>
+        <v>42500000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>293</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Purchase Price</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>293</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Initial Equity</t>
+          <t>Peak Cost</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17000000</v>
+        <v>44100000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>304</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DD / Closing Costs</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>420000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Peak Equity</t>
+          <t>Exit Price (Gross)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17850000</v>
+        <v>57800000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>399</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hold Period</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
+          <t>Cap Rate</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Equity Subtotal</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>43220000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>298</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.079</v>
+          <t>Going-In Cap Rate</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Financing Cost</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>255000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.134</v>
+          <t>Market Cap Rate</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Total Uses</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>43475000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unlevered Equity Multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.42</v>
+          <t>Exit Cap Rate</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0575</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Levered Equity Multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.71</v>
+          <t>Gross Returns</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cash-on-Cash</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.061</v>
+          <t>Unlevered IRR</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.079</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lease Term Assumption</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10-year weighted average</t>
-        </is>
+          <t>Unlevered Equity Multiple</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Downtime Assumption</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>9 months between leases</t>
-        </is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.134</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Levered Equity Multiple</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cash-on-Cash</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.061</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gross</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>25500000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Interest Rate</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gross</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>$ Per Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Initial Equity</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="C25" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Peak Equity</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>17850000</v>
+      </c>
+      <c r="C26" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lease Term Assumption</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10-year weighted average</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Downtime Assumption</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>9 months between leases</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Exit Assumption</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Sale in Year 5 at stabilized NOI</t>
         </is>
@@ -614,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:B7"/>
+  <dimension ref="A2:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -623,7 +884,7 @@
           <t>Exit Cap Rate</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -633,7 +894,7 @@
           <t>Levered IRR</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>0.081</v>
       </c>
     </row>
@@ -643,7 +904,7 @@
           <t>Unlevered IRR</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>0.052</v>
       </c>
     </row>
@@ -653,7 +914,7 @@
           <t>Levered Equity Multiple</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>1.32</v>
       </c>
     </row>
@@ -663,7 +924,7 @@
           <t>Unlevered Equity Multiple</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>1.21</v>
       </c>
     </row>
@@ -673,8 +934,21 @@
           <t>Cash-on-Cash</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>0.041</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Exit Price (Gross)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>49300000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
